--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -35,8 +35,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -71,8 +78,9 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -469,18 +477,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$2</definedName>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -476,7 +476,7 @@
     <col min="2" max="2" width="15.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14" customHeight="1">
+    <row r="1" spans="1:2" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14" customHeight="1">
+    <row r="2" spans="1:2" ht="16" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -476,7 +476,7 @@
     <col min="2" max="2" width="15.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" customHeight="1">
+    <row r="1" spans="1:2" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" customHeight="1">
+    <row r="2" spans="1:2" ht="14" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -10,19 +10,22 @@
     <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Manufacturer</t>
   </si>
   <si>
     <t>Color</t>
+  </si>
+  <si>
+    <t>Nullable Color</t>
   </si>
   <si>
     <t>BUILDYOURDREAM</t>
@@ -469,31 +472,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="19.7142857142857" customWidth="1"/>
     <col min="2" max="2" width="15.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14" customHeight="1">
+    <row r="1" spans="1:3" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="14" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:C2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -83,9 +83,26 @@
           <t xml:space="preserve">ANTIQUEWHITE</t>
         </is>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANTIQUEWHITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDYOURDREAM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANTIQUEWHITE</t>
+        </is>
+      </c>
+      <c r="C3" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
+  <autoFilter ref="A1:C3"/>
 </worksheet>
 </file>
--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </sheets>
 </workbook>
 </file>
@@ -38,9 +38,9 @@
     </border>
   </borders>
   <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -100,7 +100,6 @@
           <t xml:space="preserve">ANTIQUEWHITE</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C3"/>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -104,5 +104,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C3"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A3">
+      <formula1>"BUILDYOURDREAM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B2:B3">
+      <formula1>"ANTIQUEWHITE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C3">
+      <formula1>"ANTIQUEWHITE"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -105,13 +105,13 @@
   </sheetData>
   <autoFilter ref="A1:C3"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A3">
       <formula1>"BUILDYOURDREAM"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B3">
       <formula1>"ANTIQUEWHITE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C3">
       <formula1>"ANTIQUEWHITE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -105,13 +105,13 @@
   </sheetData>
   <autoFilter ref="A1:C3"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." sqref="A2:A3">
       <formula1>"BUILDYOURDREAM"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: ANTIQUEWHITE." sqref="B2:B3">
       <formula1>"ANTIQUEWHITE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: ANTIQUEWHITE." sqref="C2:C3">
       <formula1>"ANTIQUEWHITE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -116,4 +116,14 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/VerifyTests/Verify.OpenXml/v1/columnMetadata">
+  <sheet name="Sheet1">
+    <column index="1" property="Manufacturer"/>
+    <column index="2" property="Color"/>
+    <column index="3" property="NullableColor"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -119,7 +119,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/VerifyTests/Verify.OpenXml/v1/columnMetadata">
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Manufacturer"/>
     <column index="2" property="Color"/>

--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -104,5 +104,26 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C3"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." sqref="A2:A3">
+      <formula1>"BUILDYOURDREAM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: ANTIQUEWHITE." sqref="B2:B3">
+      <formula1>"ANTIQUEWHITE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: ANTIQUEWHITE." sqref="C2:C3">
+      <formula1>"ANTIQUEWHITE"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Manufacturer"/>
+    <column index="2" property="Color"/>
+    <column index="3" property="NullableColor"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForEnums.Test.verified.xlsx
@@ -52,7 +52,7 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
